--- a/5/search/FY3_Missile2_results/solutions_direction_180.0.xlsx
+++ b/5/search/FY3_Missile2_results/solutions_direction_180.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,72 +487,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6000</v>
+        <v>6256.090488455686</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>253.9381773049295</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6000</v>
+        <v>6256.090488455686</v>
       </c>
       <c r="I2" t="n">
-        <v>192</v>
+        <v>253.9381773049295</v>
       </c>
       <c r="J2" t="n">
-        <v>680.4</v>
+        <v>700</v>
       </c>
       <c r="K2" t="n">
-        <v>1.200000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B3" t="n">
-        <v>95.2</v>
+        <v>132</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>6248.558415265813</v>
       </c>
       <c r="F3" t="n">
-        <v>46.40000000000009</v>
+        <v>158.2341132665492</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6000</v>
+        <v>6258.915015901888</v>
       </c>
       <c r="I3" t="n">
-        <v>236.8000000000001</v>
+        <v>289.8272013193221</v>
       </c>
       <c r="J3" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.100000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -560,10 +560,10 @@
         <v>90</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>6000</v>
       </c>
       <c r="F4" t="n">
-        <v>214.4000000000001</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
@@ -581,13 +581,13 @@
         <v>6000</v>
       </c>
       <c r="I4" t="n">
-        <v>214.4000000000001</v>
+        <v>200</v>
       </c>
       <c r="J4" t="n">
         <v>700</v>
       </c>
       <c r="K4" t="n">
-        <v>2.200000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -595,10 +595,10 @@
         <v>90</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -616,327 +616,922 @@
         <v>6000</v>
       </c>
       <c r="I5" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="J5" t="n">
         <v>680.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.400000000000002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
-        <v>81.2</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>5542.710771794397</v>
+        <v>6000</v>
       </c>
       <c r="F6" t="n">
-        <v>-112.7894427722931</v>
+        <v>192</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>5491.90085754933</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
-        <v>208.0117302530077</v>
+        <v>192</v>
       </c>
       <c r="J6" t="n">
-        <v>621.6</v>
+        <v>700</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8999999999999986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B7" t="n">
-        <v>103.6</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>700</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>276</v>
+      </c>
+      <c r="J7" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>5546.214903811298</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-134.9136616016244</v>
-      </c>
-      <c r="G7" t="n">
-        <v>700</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5497.595072076795</v>
-      </c>
-      <c r="I7" t="n">
-        <v>172.0598746553444</v>
-      </c>
-      <c r="J7" t="n">
-        <v>655.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.6000000000000014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B8" t="n">
-        <v>117.6</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>5558.479365870453</v>
+        <v>6000</v>
       </c>
       <c r="F8" t="n">
-        <v>-212.3484275042833</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>5484.892593515528</v>
+        <v>6000</v>
       </c>
       <c r="I8" t="n">
-        <v>252.2601679116694</v>
+        <v>250</v>
       </c>
       <c r="J8" t="n">
-        <v>621.6</v>
+        <v>695.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99</v>
+        <v>94.5</v>
       </c>
       <c r="B9" t="n">
-        <v>120.4</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>5547.966969819749</v>
+        <v>5766.505731113934</v>
       </c>
       <c r="F9" t="n">
-        <v>-145.9757710162899</v>
+        <v>-33.17401481021079</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>5491.462841047217</v>
+        <v>5747.047875373428</v>
       </c>
       <c r="I9" t="n">
-        <v>210.7772576066739</v>
+        <v>214.061483955605</v>
       </c>
       <c r="J9" t="n">
-        <v>655.9</v>
+        <v>680.4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.899999999999999</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="B10" t="n">
-        <v>89.59999999999999</v>
+        <v>128</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5113.986473728151</v>
+        <v>5758.973657924061</v>
       </c>
       <c r="F10" t="n">
-        <v>-273.1307564785357</v>
+        <v>62.53004922816899</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>4975.546860248175</v>
+        <v>5748.930893670897</v>
       </c>
       <c r="I10" t="n">
-        <v>152.9425628216932</v>
+        <v>190.1354679460094</v>
       </c>
       <c r="J10" t="n">
-        <v>577.5</v>
+        <v>695.1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B11" t="n">
-        <v>103.6</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
         <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>4683.064358355523</v>
+        <v>5544.462837802848</v>
       </c>
       <c r="F11" t="n">
-        <v>-415.3682746343825</v>
+        <v>-123.8515521869585</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>4400.863863717421</v>
+        <v>5495.655284710297</v>
       </c>
       <c r="I11" t="n">
-        <v>138.481380801107</v>
+        <v>184.3072100787244</v>
       </c>
       <c r="J11" t="n">
-        <v>523.6</v>
+        <v>655.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6000000000000014</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>4222.537397067561</v>
+        <v>5556.977595006067</v>
       </c>
       <c r="F12" t="n">
-        <v>-553.5326090101589</v>
+        <v>-202.8666194345697</v>
       </c>
       <c r="G12" t="n">
         <v>700</v>
       </c>
       <c r="H12" t="n">
-        <v>3704.110804545599</v>
+        <v>5483.140527507077</v>
       </c>
       <c r="I12" t="n">
-        <v>160.0203800285447</v>
+        <v>263.3222773263354</v>
       </c>
       <c r="J12" t="n">
-        <v>459.9</v>
+        <v>621.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.600000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="B13" t="n">
-        <v>106.4</v>
+        <v>120</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>2556.823671940224</v>
+        <v>5549.468740684135</v>
       </c>
       <c r="F13" t="n">
-        <v>-498.3859662432337</v>
+        <v>-155.4575790860035</v>
       </c>
       <c r="G13" t="n">
         <v>700</v>
       </c>
       <c r="H13" t="n">
-        <v>1696.02958992528</v>
+        <v>5493.152333269652</v>
       </c>
       <c r="I13" t="n">
-        <v>127.0175421959578</v>
+        <v>200.110223528246</v>
       </c>
       <c r="J13" t="n">
-        <v>209.9999999999999</v>
+        <v>655.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7000000000000028</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>99</v>
+      </c>
+      <c r="B14" t="n">
+        <v>138</v>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5568.240876488963</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-273.9801799574198</v>
+      </c>
+      <c r="G14" t="n">
+        <v>700</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5481.889051786756</v>
+      </c>
+      <c r="I14" t="n">
+        <v>271.2237840510963</v>
+      </c>
+      <c r="J14" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5333.280040827534</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-222.9115073442354</v>
+      </c>
+      <c r="G15" t="n">
+        <v>700</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5238.034332374325</v>
+      </c>
+      <c r="I15" t="n">
+        <v>173.8154201780167</v>
+      </c>
+      <c r="J15" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>118</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5338.882729560076</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-246.2483854337797</v>
+      </c>
+      <c r="G16" t="n">
+        <v>700</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5228.696517820089</v>
+      </c>
+      <c r="I16" t="n">
+        <v>212.7102169939237</v>
+      </c>
+      <c r="J16" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>138</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5355.690795757701</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-316.2590197024119</v>
+      </c>
+      <c r="G17" t="n">
+        <v>700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5226.828954909241</v>
+      </c>
+      <c r="I17" t="n">
+        <v>220.4891763571056</v>
+      </c>
+      <c r="J17" t="n">
+        <v>621.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102</v>
+      </c>
+      <c r="C18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5117.447464065151</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-283.7825894610414</v>
+      </c>
+      <c r="G18" t="n">
+        <v>700</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4959.848796933928</v>
+      </c>
+      <c r="I18" t="n">
+        <v>201.2562338494869</v>
+      </c>
+      <c r="J18" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>118</v>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4916.240519542066</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-383.5731639280357</v>
+      </c>
+      <c r="G19" t="n">
+        <v>700</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4690.457294446664</v>
+      </c>
+      <c r="I19" t="n">
+        <v>161.5157602536235</v>
+      </c>
+      <c r="J19" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>136</v>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4959.101063966956</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-487.0476715693003</v>
+      </c>
+      <c r="G20" t="n">
+        <v>700</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4646.831383157042</v>
+      </c>
+      <c r="I20" t="n">
+        <v>266.8380269599097</v>
+      </c>
+      <c r="J20" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B21" t="n">
+        <v>138</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4943.793726672352</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-450.0924902688489</v>
+      </c>
+      <c r="G21" t="n">
+        <v>700</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4679.74215834044</v>
+      </c>
+      <c r="I21" t="n">
+        <v>187.3843871639389</v>
+      </c>
+      <c r="J21" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>117</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4677.97966475844</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-405.3890015634724</v>
+      </c>
+      <c r="G22" t="n">
+        <v>700</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4394.689592920963</v>
+      </c>
+      <c r="I22" t="n">
+        <v>150.5990695300692</v>
+      </c>
+      <c r="J22" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>117</v>
+      </c>
+      <c r="B23" t="n">
+        <v>120</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4692.507360750105</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-433.9012103375007</v>
+      </c>
+      <c r="G23" t="n">
+        <v>700</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4365.634200937632</v>
+      </c>
+      <c r="I23" t="n">
+        <v>207.6234870781241</v>
+      </c>
+      <c r="J23" t="n">
+        <v>523.6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>108</v>
+      </c>
+      <c r="C24" t="n">
+        <v>28</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4419.964340298971</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-421.6161429932249</v>
+      </c>
+      <c r="G24" t="n">
+        <v>700</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4024.955425373714</v>
+      </c>
+      <c r="I24" t="n">
+        <v>222.9798212584689</v>
+      </c>
+      <c r="J24" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110</v>
+      </c>
+      <c r="C25" t="n">
+        <v>28</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4189.621422939183</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-508.227657325162</v>
+      </c>
+      <c r="G25" t="n">
+        <v>700</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3737.026778673978</v>
+      </c>
+      <c r="I25" t="n">
+        <v>114.7154283435475</v>
+      </c>
+      <c r="J25" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126</v>
+      </c>
+      <c r="B26" t="n">
+        <v>126</v>
+      </c>
+      <c r="C26" t="n">
+        <v>24</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4222.537397067561</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-553.5326090101589</v>
+      </c>
+      <c r="G26" t="n">
+        <v>700</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3704.110804545599</v>
+      </c>
+      <c r="I26" t="n">
+        <v>160.0203800285447</v>
+      </c>
+      <c r="J26" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3838.636895157149</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-469.3689464830968</v>
+      </c>
+      <c r="G27" t="n">
+        <v>700</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3298.296118946436</v>
+      </c>
+      <c r="I27" t="n">
+        <v>163.288816896129</v>
+      </c>
+      <c r="J27" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B28" t="n">
+        <v>132</v>
+      </c>
+      <c r="C28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3942.548582889979</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-591.0339009791014</v>
+      </c>
+      <c r="G28" t="n">
+        <v>700</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3256.731443853305</v>
+      </c>
+      <c r="I28" t="n">
+        <v>211.9547986945314</v>
+      </c>
+      <c r="J28" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B29" t="n">
+        <v>116</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3177.373055692685</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-589.2488445983577</v>
+      </c>
+      <c r="G29" t="n">
+        <v>700</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2383.509227606253</v>
+      </c>
+      <c r="I29" t="n">
+        <v>88.77491785835423</v>
+      </c>
+      <c r="J29" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>130</v>
+      </c>
+      <c r="C30" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3232.122285215888</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-636.0091040781308</v>
+      </c>
+      <c r="G30" t="n">
+        <v>700</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2342.447305463852</v>
+      </c>
+      <c r="I30" t="n">
+        <v>123.8451124681842</v>
+      </c>
+      <c r="J30" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>144</v>
       </c>
-      <c r="B14" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>32</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="B31" t="n">
+        <v>116</v>
+      </c>
+      <c r="C31" t="n">
+        <v>36</v>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
-        <v>2665.555555984217</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-577.3843041513419</v>
-      </c>
-      <c r="G14" t="n">
-        <v>700</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1623.541667229285</v>
-      </c>
-      <c r="I14" t="n">
-        <v>179.6831008013637</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="E31" t="n">
+        <v>2621.54503149022</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-545.4087864266317</v>
+      </c>
+      <c r="G31" t="n">
+        <v>700</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1683.085318015281</v>
+      </c>
+      <c r="I31" t="n">
+        <v>136.4221062326374</v>
+      </c>
+      <c r="J31" t="n">
         <v>209.9999999999999</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
     </row>
